--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Games\tofoldman-Copy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\YAD\YADP\Python\tof\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB03A666-17A5-4F14-84AC-392364334501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CC7A79-2C24-4799-BF5B-E3B1F9339F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="450" windowWidth="18330" windowHeight="10050" xr2:uid="{8B64225B-6660-45BC-ACE7-6FE2268E8CAC}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="14160" windowHeight="10320" xr2:uid="{8B64225B-6660-45BC-ACE7-6FE2268E8CAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="70">
   <si>
     <t>s.no</t>
   </si>
@@ -53,301 +53,199 @@
     <t>server</t>
   </si>
   <si>
+    <t>aestral_noa</t>
+  </si>
+  <si>
+    <t>Frankster</t>
+  </si>
+  <si>
+    <t>Gojo Satoru</t>
+  </si>
+  <si>
+    <t>Uci</t>
+  </si>
+  <si>
+    <t>Lero God</t>
+  </si>
+  <si>
+    <t>Salaciousrumour</t>
+  </si>
+  <si>
+    <t>Ereon#a</t>
+  </si>
+  <si>
+    <t>NotUci</t>
+  </si>
+  <si>
+    <t>Suka susu</t>
+  </si>
+  <si>
+    <t>Kuromiya Konata</t>
+  </si>
+  <si>
+    <t>Narrow</t>
+  </si>
+  <si>
+    <t>Argen</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+gfranky@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+ggojo@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+guci@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+glero@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+gsala@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+gyato@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+gereon@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+gnotuci@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+gnes@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+gkona@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+gnarrow@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+gargen@gmail.com</t>
+  </si>
+  <si>
+    <t>Yato</t>
+  </si>
+  <si>
+    <t>yimytp1gl</t>
+  </si>
+  <si>
+    <t>Fauzialriduan212@gmail.com</t>
+  </si>
+  <si>
+    <t>Fauzi12345</t>
+  </si>
+  <si>
+    <t>Bun</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+gbun@gmail.com</t>
+  </si>
+  <si>
+    <t>Lucy</t>
+  </si>
+  <si>
+    <t>Bee nu</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+gbeenu@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+by084@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+by085@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+by086@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+by087@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+by088@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+by089@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+by090@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+by091@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+by092@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+by093@gmail.com</t>
+  </si>
+  <si>
+    <t>kisaaa</t>
+  </si>
+  <si>
+    <t>amane_k</t>
+  </si>
+  <si>
+    <t>naroqq</t>
+  </si>
+  <si>
+    <t>kylon44</t>
+  </si>
+  <si>
+    <t>thopiita.</t>
+  </si>
+  <si>
+    <t>tatssumaki</t>
+  </si>
+  <si>
+    <t>greemjawa</t>
+  </si>
+  <si>
+    <t>dynasty8</t>
+  </si>
+  <si>
+    <t>Shinitai_Chan</t>
+  </si>
+  <si>
+    <t>blobstar</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+ytrap@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+yegirl@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+yfemboy@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+yloli@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+ymommy@gmail.com</t>
+  </si>
+  <si>
+    <t>yiskaailhsfm+yghost@gmail.com</t>
+  </si>
+  <si>
     <t>TrapYuuko</t>
   </si>
   <si>
-    <t>trapfranky@tempemail.co</t>
-  </si>
-  <si>
-    <t>emoyuuko5427</t>
-  </si>
-  <si>
-    <t>aestral_noa</t>
-  </si>
-  <si>
     <t>eGirlYuuko</t>
   </si>
   <si>
-    <t>egirlfranky@tempemail.co</t>
-  </si>
-  <si>
     <t>FemboyYuuko</t>
   </si>
   <si>
-    <t>femboyfranky@tempemail.co</t>
-  </si>
-  <si>
     <t>LoliYuuko</t>
   </si>
   <si>
-    <t>lolifranky@tempemail.co</t>
-  </si>
-  <si>
     <t>MommyYuuko</t>
   </si>
   <si>
-    <t>mommyfranky@tempemail.co</t>
-  </si>
-  <si>
-    <t>Frankster</t>
-  </si>
-  <si>
-    <t>shotthepickup@gmail.com</t>
-  </si>
-  <si>
-    <t>franky00</t>
-  </si>
-  <si>
-    <t>Gojo Satoru</t>
-  </si>
-  <si>
-    <t>shaream.gaming@gmail.com</t>
-  </si>
-  <si>
-    <t>Iamacoolboy16!</t>
-  </si>
-  <si>
-    <t>Uci</t>
-  </si>
-  <si>
-    <t>kog434@gmail.com</t>
-  </si>
-  <si>
-    <t>5B6o%xY$$48e$3A*z$P</t>
-  </si>
-  <si>
-    <t>Lero God</t>
-  </si>
-  <si>
-    <t>threshgametof@gmail.com</t>
-  </si>
-  <si>
-    <t>C0caxpassay</t>
-  </si>
-  <si>
-    <t>Salaciousrumour</t>
-  </si>
-  <si>
-    <t>crawfoliam@gmail.com</t>
-  </si>
-  <si>
-    <t>P4nduhT0f():!</t>
-  </si>
-  <si>
-    <t>Norie</t>
-  </si>
-  <si>
-    <t>Parshant009@gmail.com</t>
-  </si>
-  <si>
-    <t>Gametof@123</t>
-  </si>
-  <si>
-    <t>Ereon#a</t>
-  </si>
-  <si>
-    <t>solopepe1731@gmail.com</t>
-  </si>
-  <si>
-    <t>Ereonmain</t>
-  </si>
-  <si>
-    <t>NotUci</t>
-  </si>
-  <si>
-    <t>tanakron0992428281@hotmail.com</t>
-  </si>
-  <si>
-    <t>Jeanny44774477</t>
-  </si>
-  <si>
-    <t>Suka susu</t>
-  </si>
-  <si>
-    <t>sudarwijayans@gmail.com</t>
-  </si>
-  <si>
-    <t>AsenMaxx123</t>
-  </si>
-  <si>
-    <t>Kuromiya Konata</t>
-  </si>
-  <si>
-    <t>games@konata.moe</t>
-  </si>
-  <si>
-    <t>7KBvFQPRDg@docs3#3f</t>
-  </si>
-  <si>
-    <t>Mbun</t>
-  </si>
-  <si>
-    <t>firmansyahphoenix@gmail.com</t>
-  </si>
-  <si>
-    <t>Embun12321</t>
-  </si>
-  <si>
-    <t>Narrow</t>
-  </si>
-  <si>
-    <t>cocwarrior223@gmail.com</t>
-  </si>
-  <si>
-    <t>TowerOfFantasy@123</t>
-  </si>
-  <si>
-    <t>Argen</t>
-  </si>
-  <si>
-    <t>asseyvers@gmail.com</t>
-  </si>
-  <si>
-    <t>nonchara10Rina</t>
-  </si>
-  <si>
-    <t>lucy</t>
-  </si>
-  <si>
-    <t>Fauzialriduan212@gmail.com</t>
-  </si>
-  <si>
-    <t>Fauzi12345</t>
-  </si>
-  <si>
-    <t>bee nu</t>
-  </si>
-  <si>
-    <t>Kholisdwi999@gmail.com</t>
-  </si>
-  <si>
-    <t>tsina2w@1</t>
-  </si>
-  <si>
-    <t>Sinon</t>
-  </si>
-  <si>
-    <t>asadashinosinon2107@gmail.com</t>
-  </si>
-  <si>
-    <t>S1n0n#K@w@11</t>
-  </si>
-  <si>
     <t>Yuuko Ghost</t>
-  </si>
-  <si>
-    <t>smartrandomgamer@gmail.com</t>
-  </si>
-  <si>
-    <t>Aki-to</t>
-  </si>
-  <si>
-    <t>pikukun9937@gmail.com</t>
-  </si>
-  <si>
-    <t>IAMGAY69</t>
-  </si>
-  <si>
-    <t>Gleaming Gojo</t>
-  </si>
-  <si>
-    <t>kisaaa</t>
-  </si>
-  <si>
-    <t>amane_k</t>
-  </si>
-  <si>
-    <t>naroqq</t>
-  </si>
-  <si>
-    <t>kylon44</t>
-  </si>
-  <si>
-    <t>thopiita.</t>
-  </si>
-  <si>
-    <t>tatssumaki</t>
-  </si>
-  <si>
-    <t>greemjawa</t>
-  </si>
-  <si>
-    <t>dynasty8</t>
-  </si>
-  <si>
-    <t>Shinitai_Chan</t>
-  </si>
-  <si>
-    <t>blobstar</t>
-  </si>
-  <si>
-    <t>kawaikochan69696@gmail.com</t>
-  </si>
-  <si>
-    <t>HuTaoSimp69</t>
-  </si>
-  <si>
-    <t>aeria</t>
-  </si>
-  <si>
-    <t>mbkisakiivk@gmail.com</t>
-  </si>
-  <si>
-    <t>tofkisa123</t>
-  </si>
-  <si>
-    <t>mbkisakiivk+001@gmail.com</t>
-  </si>
-  <si>
-    <t>mbkisakiivk+002@gmail.com</t>
-  </si>
-  <si>
-    <t>mbkisakiivk+003@gmail.com</t>
-  </si>
-  <si>
-    <t>mbkisakiivk+004@gmail.com</t>
-  </si>
-  <si>
-    <t>mbkisakiivk+005@gmail.com</t>
-  </si>
-  <si>
-    <t>mbkisakiivk+006@gmail.com</t>
-  </si>
-  <si>
-    <t>mbkisakiivk+007@gmail.com</t>
-  </si>
-  <si>
-    <t>mbkisakiivk+008@gmail.com</t>
-  </si>
-  <si>
-    <t>mbkisakiivk+009@gmail.com</t>
-  </si>
-  <si>
-    <t>mbkisakiivk+010@gmail.com</t>
-  </si>
-  <si>
-    <t>sheroyaksha</t>
-  </si>
-  <si>
-    <t>infinitybros2003@gmail.com</t>
-  </si>
-  <si>
-    <t>rakshit@2003</t>
-  </si>
-  <si>
-    <t>stardust</t>
-  </si>
-  <si>
-    <t>asuna</t>
-  </si>
-  <si>
-    <t>Dalisayjamesivan+2@gmail.com</t>
-  </si>
-  <si>
-    <t>*(akosidaved)*</t>
-  </si>
-  <si>
-    <t>MizushiYuuko</t>
   </si>
 </sst>
 </file>
@@ -738,18 +636,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16AA823D-0523-450D-974F-45D7F4011F57}">
-  <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.88671875" style="1" customWidth="1"/>
     <col min="3" max="3" width="37" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.42578125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="24.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -766,663 +664,536 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>32</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
-        <v>33</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
-        <v>34</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
-        <v>35</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
-        <v>36</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
-        <v>37</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>83</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="C18" r:id="rId1" xr:uid="{570F0C75-3A9D-4D1B-8B92-140987891261}"/>
-    <hyperlink ref="D18" r:id="rId2" xr:uid="{7A566CCE-BACA-4760-A45B-0C16A422AC2B}"/>
-    <hyperlink ref="C19" r:id="rId3" xr:uid="{57C0669C-D17D-4C75-AECD-F4AEABB1B803}"/>
-    <hyperlink ref="D19" r:id="rId4" xr:uid="{655DF325-B5BC-4556-9DFB-4AE7EB93B48A}"/>
-    <hyperlink ref="C5" r:id="rId5" xr:uid="{CCBEEDF6-BDED-44BF-8380-72E55F170B57}"/>
-    <hyperlink ref="C7" r:id="rId6" xr:uid="{58A13706-603F-4164-99F6-BB33CD5D0277}"/>
-    <hyperlink ref="C8" r:id="rId7" xr:uid="{65B1E0B3-466E-4892-A03E-79B1A8187C9B}"/>
-    <hyperlink ref="D9" r:id="rId8" xr:uid="{6AAC4FAD-F5E1-4BFA-A41E-0A67938E9B79}"/>
-    <hyperlink ref="C10" r:id="rId9" xr:uid="{9B73FB52-CD1B-41B2-94B4-C9E4B381001D}"/>
-    <hyperlink ref="C11" r:id="rId10" xr:uid="{759B7C57-1CA2-4A67-8AD2-1C32D23FDE3D}"/>
-    <hyperlink ref="C13" r:id="rId11" xr:uid="{7413C46E-43DE-4B26-B769-2AB2DFA48825}"/>
-    <hyperlink ref="D13" r:id="rId12" xr:uid="{214149F7-5981-40C2-8826-AE4ED8595830}"/>
-    <hyperlink ref="C3" r:id="rId13" xr:uid="{DD49969F-ED4E-4AA5-8261-05295D0CFE14}"/>
-    <hyperlink ref="C16" r:id="rId14" xr:uid="{6B33FD52-A81A-431D-BA13-F1FD9C073A23}"/>
-    <hyperlink ref="C28" r:id="rId15" xr:uid="{C087539B-B97C-4105-B1D0-931B05E22829}"/>
-    <hyperlink ref="C29" r:id="rId16" xr:uid="{7D8C05EE-1D46-44A7-893A-C1499D58967C}"/>
-    <hyperlink ref="C30" r:id="rId17" xr:uid="{6CE17BD5-2FD2-42D1-92FB-21AF5B0C39A2}"/>
-    <hyperlink ref="C31" r:id="rId18" xr:uid="{32F2CAA6-7229-44B8-BA17-2F86E57B4AAB}"/>
-    <hyperlink ref="C32" r:id="rId19" xr:uid="{B203AFA7-4C0C-48BE-8913-A77AF86B33E3}"/>
-    <hyperlink ref="C33" r:id="rId20" xr:uid="{4F2E790E-F3E5-4A33-937E-8148294A51F6}"/>
-    <hyperlink ref="C34" r:id="rId21" xr:uid="{8F3418DE-50CC-4DB0-B730-0463F1D7508F}"/>
-    <hyperlink ref="C35" r:id="rId22" xr:uid="{4FA1A8C8-8B56-43FC-8ABC-DD79AEC78E7C}"/>
-    <hyperlink ref="C36" r:id="rId23" xr:uid="{FF0EE393-8CC2-4C37-9CBE-87D48E61B300}"/>
-    <hyperlink ref="C2" r:id="rId24" xr:uid="{5A231EA5-976A-4F6A-AC69-5EB892432098}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>